--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
   <si>
     <t>Date</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-23</t>
+    <t>2025-11-25</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
   </si>
   <si>
     <t>2025-11-26</t>
@@ -363,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -398,11 +392,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>0.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -525,7 +519,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -539,7 +533,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -679,7 +673,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -693,7 +687,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -721,7 +715,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -735,7 +729,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -875,7 +869,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -889,7 +883,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -1113,7 +1107,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1127,7 +1121,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1211,7 +1205,7 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>0.0</v>
@@ -1225,7 +1219,7 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1553,34 +1547,6 @@
         <v>0.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1596,21 +1562,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1628,18 +1594,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,259 +28,274 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-25</t>
+    <t>2025-11-27</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>2025-11-29</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-02</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>2025-12-06</t>
+  </si>
+  <si>
+    <t>2025-12-07</t>
+  </si>
+  <si>
+    <t>2025-12-08</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>2025-12-13</t>
+  </si>
+  <si>
+    <t>2025-12-14</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2025-12-20</t>
+  </si>
+  <si>
+    <t>2025-12-21</t>
+  </si>
+  <si>
+    <t>2025-12-22</t>
+  </si>
+  <si>
+    <t>2025-12-23</t>
+  </si>
+  <si>
+    <t>2025-12-24</t>
+  </si>
+  <si>
+    <t>2025-12-25</t>
+  </si>
+  <si>
+    <t>2025-12-26</t>
+  </si>
+  <si>
+    <t>2025-12-27</t>
+  </si>
+  <si>
+    <t>2025-12-28</t>
+  </si>
+  <si>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>2026-01-03</t>
+  </si>
+  <si>
+    <t>2026-01-04</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2026-01-06</t>
+  </si>
+  <si>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-01-11</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-13</t>
+  </si>
+  <si>
+    <t>2026-01-14</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-01-16</t>
+  </si>
+  <si>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>2026-01-18</t>
+  </si>
+  <si>
+    <t>2026-01-19</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>2026-01-21</t>
+  </si>
+  <si>
+    <t>2026-01-22</t>
+  </si>
+  <si>
+    <t>2026-01-23</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>2026-01-27</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>2026-02-06</t>
+  </si>
+  <si>
+    <t>2026-02-07</t>
+  </si>
+  <si>
+    <t>2026-02-08</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-02-11</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>2025-11-29</t>
-  </si>
-  <si>
-    <t>2025-11-30</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
-  </si>
-  <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
-    <t>2025-12-04</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>2025-12-06</t>
-  </si>
-  <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
   </si>
   <si>
     <t>Reason</t>
@@ -357,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -378,11 +393,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -390,13 +405,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -404,7 +419,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>6.0</v>
@@ -418,7 +433,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>6.0</v>
@@ -432,7 +447,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>6.0</v>
@@ -446,7 +461,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>6.0</v>
@@ -460,7 +475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>6.0</v>
@@ -474,7 +489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>6.0</v>
@@ -488,10 +503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -502,10 +517,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -516,7 +531,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>4.0</v>
@@ -530,7 +545,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>4.0</v>
@@ -544,7 +559,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>4.0</v>
@@ -558,7 +573,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>4.0</v>
@@ -572,7 +587,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>4.0</v>
@@ -586,7 +601,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>4.0</v>
@@ -600,7 +615,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>4.0</v>
@@ -614,7 +629,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>4.0</v>
@@ -628,7 +643,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>4.0</v>
@@ -642,10 +657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -656,10 +671,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -670,7 +685,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>5.0</v>
@@ -684,10 +699,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -698,10 +713,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -712,7 +727,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>4.0</v>
@@ -726,7 +741,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>4.0</v>
@@ -740,7 +755,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>4.0</v>
@@ -754,7 +769,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>4.0</v>
@@ -768,7 +783,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>4.0</v>
@@ -782,7 +797,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>4.0</v>
@@ -796,7 +811,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>4.0</v>
@@ -810,7 +825,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>4.0</v>
@@ -824,7 +839,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>4.0</v>
@@ -838,10 +853,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -852,10 +867,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -866,7 +881,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>3.0</v>
@@ -880,7 +895,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>3.0</v>
@@ -894,7 +909,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>3.0</v>
@@ -908,7 +923,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>3.0</v>
@@ -922,7 +937,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>3.0</v>
@@ -936,7 +951,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>3.0</v>
@@ -950,7 +965,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>3.0</v>
@@ -964,7 +979,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>3.0</v>
@@ -978,7 +993,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>3.0</v>
@@ -992,7 +1007,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>3.0</v>
@@ -1006,7 +1021,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>3.0</v>
@@ -1020,7 +1035,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>3.0</v>
@@ -1034,7 +1049,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>3.0</v>
@@ -1048,7 +1063,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>3.0</v>
@@ -1062,7 +1077,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>3.0</v>
@@ -1076,10 +1091,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1090,10 +1105,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1104,7 +1119,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>1.0</v>
@@ -1118,7 +1133,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>1.0</v>
@@ -1132,7 +1147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>1.0</v>
@@ -1146,7 +1161,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>1.0</v>
@@ -1160,7 +1175,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>1.0</v>
@@ -1174,10 +1189,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>0.0</v>
@@ -1188,10 +1203,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>0.0</v>
@@ -1202,7 +1217,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>0.0</v>
@@ -1216,7 +1231,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>0.0</v>
@@ -1230,7 +1245,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>0.0</v>
@@ -1244,7 +1259,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>0.0</v>
@@ -1258,7 +1273,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>0.0</v>
@@ -1272,7 +1287,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>0.0</v>
@@ -1286,7 +1301,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>0.0</v>
@@ -1300,7 +1315,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>0.0</v>
@@ -1314,7 +1329,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>0.0</v>
@@ -1328,7 +1343,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>0.0</v>
@@ -1342,7 +1357,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>0.0</v>
@@ -1356,7 +1371,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>0.0</v>
@@ -1370,7 +1385,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>0.0</v>
@@ -1384,7 +1399,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>0.0</v>
@@ -1398,7 +1413,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>0.0</v>
@@ -1412,7 +1427,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>0.0</v>
@@ -1426,7 +1441,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>0.0</v>
@@ -1440,7 +1455,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>0.0</v>
@@ -1454,7 +1469,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>0.0</v>
@@ -1468,7 +1483,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>0.0</v>
@@ -1482,7 +1497,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>0.0</v>
@@ -1496,7 +1511,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>0.0</v>
@@ -1510,7 +1525,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>0.0</v>
@@ -1524,7 +1539,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>0.0</v>
@@ -1538,16 +1553,86 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>0.0</v>
+      <c r="B86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1562,21 +1647,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1594,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -28,12 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
     <t>2025-11-28</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2025-11-29</t>
   </si>
   <si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>2026-02-23</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Reason</t>
@@ -372,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -393,11 +390,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>0.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -405,13 +402,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>0.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -419,13 +416,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>0.0</v>
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -433,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>6.0</v>
@@ -447,7 +444,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>6.0</v>
@@ -461,7 +458,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>6.0</v>
@@ -475,7 +472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>6.0</v>
@@ -489,10 +486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -503,7 +500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>4.0</v>
@@ -517,7 +514,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>4.0</v>
@@ -531,7 +528,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>4.0</v>
@@ -545,7 +542,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>4.0</v>
@@ -559,7 +556,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>4.0</v>
@@ -573,7 +570,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>4.0</v>
@@ -587,7 +584,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>4.0</v>
@@ -601,7 +598,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>4.0</v>
@@ -615,7 +612,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>4.0</v>
@@ -629,7 +626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>4.0</v>
@@ -643,10 +640,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -657,7 +654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>5.0</v>
@@ -671,7 +668,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>5.0</v>
@@ -685,10 +682,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -699,7 +696,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>4.0</v>
@@ -713,7 +710,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>4.0</v>
@@ -727,7 +724,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>4.0</v>
@@ -741,7 +738,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>4.0</v>
@@ -755,7 +752,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>4.0</v>
@@ -769,7 +766,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>4.0</v>
@@ -783,7 +780,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>4.0</v>
@@ -797,7 +794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>4.0</v>
@@ -811,7 +808,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>4.0</v>
@@ -825,7 +822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>4.0</v>
@@ -839,10 +836,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -853,7 +850,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>3.0</v>
@@ -867,7 +864,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>3.0</v>
@@ -881,7 +878,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>3.0</v>
@@ -895,7 +892,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>3.0</v>
@@ -909,7 +906,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>3.0</v>
@@ -923,7 +920,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>3.0</v>
@@ -937,7 +934,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>3.0</v>
@@ -951,7 +948,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>3.0</v>
@@ -965,7 +962,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>3.0</v>
@@ -979,7 +976,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>3.0</v>
@@ -993,7 +990,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>3.0</v>
@@ -1007,7 +1004,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>3.0</v>
@@ -1021,7 +1018,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>3.0</v>
@@ -1035,7 +1032,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>3.0</v>
@@ -1049,7 +1046,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>3.0</v>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>3.0</v>
@@ -1077,10 +1074,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1091,7 +1088,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>1.0</v>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>1.0</v>
@@ -1119,7 +1116,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>1.0</v>
@@ -1133,7 +1130,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>1.0</v>
@@ -1147,7 +1144,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>1.0</v>
@@ -1161,7 +1158,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>1.0</v>
@@ -1175,10 +1172,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>0.0</v>
@@ -1189,7 +1186,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>0.0</v>
@@ -1203,7 +1200,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>0.0</v>
@@ -1217,7 +1214,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>0.0</v>
@@ -1231,7 +1228,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>0.0</v>
@@ -1245,7 +1242,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>0.0</v>
@@ -1259,7 +1256,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>0.0</v>
@@ -1273,7 +1270,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>0.0</v>
@@ -1287,7 +1284,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>0.0</v>
@@ -1301,7 +1298,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>0.0</v>
@@ -1315,7 +1312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>0.0</v>
@@ -1329,7 +1326,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>0.0</v>
@@ -1343,7 +1340,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>0.0</v>
@@ -1357,7 +1354,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>0.0</v>
@@ -1371,7 +1368,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>0.0</v>
@@ -1385,7 +1382,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>0.0</v>
@@ -1399,7 +1396,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>0.0</v>
@@ -1413,7 +1410,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>0.0</v>
@@ -1427,7 +1424,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>0.0</v>
@@ -1441,7 +1438,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>0.0</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>0.0</v>
@@ -1469,7 +1466,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>0.0</v>
@@ -1483,7 +1480,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>0.0</v>
@@ -1497,7 +1494,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>0.0</v>
@@ -1511,7 +1508,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>0.0</v>
@@ -1525,7 +1522,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>0.0</v>
@@ -1539,7 +1536,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>0.0</v>
@@ -1553,7 +1550,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>0.0</v>
@@ -1567,7 +1564,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>0.0</v>
@@ -1581,7 +1578,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>0.0</v>
@@ -1595,7 +1592,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>0.0</v>
@@ -1609,7 +1606,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="n" s="0">
         <v>0.0</v>
@@ -1619,20 +1616,6 @@
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1647,21 +1630,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>97</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1679,18 +1662,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>101</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,13 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-28</t>
+    <t>2025-11-29</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-29</t>
   </si>
   <si>
     <t>2025-11-30</t>
@@ -369,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -418,11 +415,11 @@
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>0.0</v>
@@ -475,7 +472,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -629,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -671,7 +668,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -825,7 +822,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -1063,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1161,7 +1158,7 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>0.0</v>
@@ -1601,20 +1598,6 @@
         <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1630,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1662,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,15 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-29</t>
+    <t>2025-11-30</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-11-30</t>
-  </si>
-  <si>
     <t>2025-12-01</t>
   </si>
   <si>
@@ -290,6 +287,15 @@
   </si>
   <si>
     <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,11 +407,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -458,7 +464,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -612,7 +618,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -654,7 +660,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -808,7 +814,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -1046,7 +1052,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>
@@ -1144,7 +1150,7 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>0.0</v>
@@ -1599,6 +1605,34 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1613,21 +1647,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1645,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,16 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-30</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
   </si>
   <si>
     <t>2025-12-03</t>
@@ -372,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -407,11 +401,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>0.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -436,7 +430,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -450,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -590,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -604,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -632,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -646,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -786,7 +780,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -800,7 +794,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -1024,7 +1018,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1038,7 +1032,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1122,7 +1116,7 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>0.0</v>
@@ -1136,7 +1130,7 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>0.0</v>
@@ -1605,34 +1599,6 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1647,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1679,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -28,13 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-02</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-03</t>
   </si>
   <si>
     <t>2025-12-04</t>
@@ -366,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,11 +398,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -416,7 +413,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -570,7 +567,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -612,7 +609,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -766,7 +763,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -1004,7 +1001,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1102,7 +1099,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>0.0</v>
@@ -1584,20 +1581,6 @@
         <v>0.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1613,21 +1596,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1645,18 +1628,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>97</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -28,12 +28,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-03</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>2025-12-04</t>
   </si>
   <si>
@@ -287,6 +281,18 @@
   </si>
   <si>
     <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
   </si>
   <si>
     <t>Reason</t>
@@ -363,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -384,11 +390,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -396,10 +402,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -410,7 +416,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>4.0</v>
@@ -424,7 +430,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>4.0</v>
@@ -438,7 +444,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>4.0</v>
@@ -452,7 +458,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>4.0</v>
@@ -466,7 +472,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>4.0</v>
@@ -480,7 +486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>4.0</v>
@@ -494,7 +500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>4.0</v>
@@ -508,7 +514,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>4.0</v>
@@ -522,7 +528,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>4.0</v>
@@ -536,7 +542,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>4.0</v>
@@ -550,10 +556,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -564,7 +570,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>5.0</v>
@@ -578,7 +584,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>5.0</v>
@@ -592,10 +598,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -606,7 +612,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>4.0</v>
@@ -620,7 +626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>4.0</v>
@@ -634,7 +640,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>4.0</v>
@@ -648,7 +654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>4.0</v>
@@ -662,7 +668,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>4.0</v>
@@ -676,7 +682,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>4.0</v>
@@ -690,7 +696,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>4.0</v>
@@ -704,7 +710,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>4.0</v>
@@ -718,7 +724,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>4.0</v>
@@ -732,7 +738,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>4.0</v>
@@ -746,10 +752,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -760,7 +766,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>3.0</v>
@@ -774,7 +780,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>3.0</v>
@@ -788,7 +794,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>3.0</v>
@@ -802,7 +808,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>3.0</v>
@@ -816,7 +822,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>3.0</v>
@@ -830,7 +836,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>3.0</v>
@@ -844,7 +850,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>3.0</v>
@@ -858,7 +864,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>3.0</v>
@@ -872,7 +878,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>3.0</v>
@@ -886,7 +892,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>3.0</v>
@@ -900,7 +906,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>3.0</v>
@@ -914,7 +920,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>3.0</v>
@@ -928,7 +934,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>3.0</v>
@@ -942,7 +948,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>3.0</v>
@@ -956,7 +962,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>3.0</v>
@@ -970,7 +976,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>3.0</v>
@@ -984,10 +990,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -998,7 +1004,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>1.0</v>
@@ -1012,7 +1018,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>1.0</v>
@@ -1026,7 +1032,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>1.0</v>
@@ -1040,7 +1046,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>1.0</v>
@@ -1054,7 +1060,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>1.0</v>
@@ -1068,7 +1074,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>1.0</v>
@@ -1082,10 +1088,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>0.0</v>
@@ -1096,7 +1102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>0.0</v>
@@ -1110,7 +1116,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>0.0</v>
@@ -1124,7 +1130,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>0.0</v>
@@ -1138,7 +1144,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>0.0</v>
@@ -1152,7 +1158,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>0.0</v>
@@ -1166,7 +1172,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>0.0</v>
@@ -1180,7 +1186,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>0.0</v>
@@ -1194,7 +1200,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>0.0</v>
@@ -1208,7 +1214,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>0.0</v>
@@ -1222,7 +1228,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>0.0</v>
@@ -1236,7 +1242,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>0.0</v>
@@ -1250,7 +1256,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>0.0</v>
@@ -1264,7 +1270,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>0.0</v>
@@ -1278,7 +1284,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>0.0</v>
@@ -1292,7 +1298,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>0.0</v>
@@ -1306,7 +1312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>0.0</v>
@@ -1320,7 +1326,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>0.0</v>
@@ -1334,7 +1340,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>0.0</v>
@@ -1348,7 +1354,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>0.0</v>
@@ -1362,7 +1368,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>0.0</v>
@@ -1376,7 +1382,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>0.0</v>
@@ -1390,7 +1396,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>0.0</v>
@@ -1404,7 +1410,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>0.0</v>
@@ -1418,7 +1424,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>0.0</v>
@@ -1432,7 +1438,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>0.0</v>
@@ -1446,7 +1452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>0.0</v>
@@ -1460,7 +1466,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>0.0</v>
@@ -1474,7 +1480,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>0.0</v>
@@ -1488,7 +1494,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>0.0</v>
@@ -1502,7 +1508,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>0.0</v>
@@ -1516,7 +1522,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>0.0</v>
@@ -1530,7 +1536,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>0.0</v>
@@ -1544,7 +1550,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>0.0</v>
@@ -1558,7 +1564,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>0.0</v>
@@ -1572,15 +1578,57 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
+      <c r="B88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1596,21 +1644,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1628,18 +1676,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -28,13 +28,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-04</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
     <t>2025-12-06</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2025-12-07</t>
@@ -369,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -390,11 +387,11 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>0.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
@@ -402,13 +399,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>0.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -416,7 +413,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
         <v>4.0</v>
@@ -430,7 +427,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>4.0</v>
@@ -444,7 +441,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>4.0</v>
@@ -458,7 +455,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>4.0</v>
@@ -472,7 +469,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>4.0</v>
@@ -486,7 +483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>4.0</v>
@@ -500,7 +497,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>4.0</v>
@@ -514,7 +511,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>4.0</v>
@@ -528,10 +525,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -542,10 +539,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -556,7 +553,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>5.0</v>
@@ -570,10 +567,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -584,10 +581,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -598,7 +595,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
         <v>4.0</v>
@@ -612,7 +609,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
         <v>4.0</v>
@@ -626,7 +623,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>4.0</v>
@@ -640,7 +637,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>4.0</v>
@@ -654,7 +651,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
         <v>4.0</v>
@@ -668,7 +665,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>4.0</v>
@@ -682,7 +679,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>4.0</v>
@@ -696,7 +693,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
         <v>4.0</v>
@@ -710,7 +707,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
         <v>4.0</v>
@@ -724,10 +721,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -738,10 +735,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -752,7 +749,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
         <v>3.0</v>
@@ -766,7 +763,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>3.0</v>
@@ -780,7 +777,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>3.0</v>
@@ -794,7 +791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>3.0</v>
@@ -808,7 +805,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>3.0</v>
@@ -822,7 +819,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>3.0</v>
@@ -836,7 +833,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>3.0</v>
@@ -850,7 +847,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>3.0</v>
@@ -864,7 +861,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>3.0</v>
@@ -878,7 +875,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>3.0</v>
@@ -892,7 +889,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>3.0</v>
@@ -906,7 +903,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>3.0</v>
@@ -920,7 +917,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>3.0</v>
@@ -934,7 +931,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>3.0</v>
@@ -948,7 +945,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>3.0</v>
@@ -962,10 +959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -976,10 +973,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -990,7 +987,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>1.0</v>
@@ -1004,7 +1001,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>1.0</v>
@@ -1018,7 +1015,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>1.0</v>
@@ -1032,7 +1029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>1.0</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>1.0</v>
@@ -1060,10 +1057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>0.0</v>
@@ -1074,10 +1071,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>0.0</v>
@@ -1088,7 +1085,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>0.0</v>
@@ -1102,7 +1099,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>0.0</v>
@@ -1116,7 +1113,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>0.0</v>
@@ -1130,7 +1127,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>0.0</v>
@@ -1144,7 +1141,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>0.0</v>
@@ -1158,7 +1155,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>0.0</v>
@@ -1172,7 +1169,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>0.0</v>
@@ -1186,7 +1183,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>0.0</v>
@@ -1200,7 +1197,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>0.0</v>
@@ -1214,7 +1211,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>0.0</v>
@@ -1228,7 +1225,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>0.0</v>
@@ -1242,7 +1239,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>0.0</v>
@@ -1256,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>0.0</v>
@@ -1270,7 +1267,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>0.0</v>
@@ -1284,7 +1281,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>0.0</v>
@@ -1298,7 +1295,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>0.0</v>
@@ -1312,7 +1309,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>0.0</v>
@@ -1326,7 +1323,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>0.0</v>
@@ -1340,7 +1337,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>0.0</v>
@@ -1354,7 +1351,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>0.0</v>
@@ -1368,7 +1365,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>0.0</v>
@@ -1382,7 +1379,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>0.0</v>
@@ -1396,7 +1393,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>0.0</v>
@@ -1410,7 +1407,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>0.0</v>
@@ -1424,7 +1421,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>0.0</v>
@@ -1438,7 +1435,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>0.0</v>
@@ -1452,7 +1449,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>0.0</v>
@@ -1466,7 +1463,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>0.0</v>
@@ -1480,7 +1477,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
         <v>0.0</v>
@@ -1494,7 +1491,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
         <v>0.0</v>
@@ -1508,7 +1505,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>0.0</v>
@@ -1522,7 +1519,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>0.0</v>
@@ -1536,7 +1533,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
         <v>0.0</v>
@@ -1550,7 +1547,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
         <v>0.0</v>
@@ -1564,7 +1561,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
         <v>0.0</v>
@@ -1578,7 +1575,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
         <v>0.0</v>
@@ -1592,7 +1589,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="n" s="0">
         <v>0.0</v>
@@ -1601,34 +1598,6 @@
         <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1644,21 +1613,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1676,18 +1645,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -28,42 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-16</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
     <t>2025-12-17</t>
   </si>
   <si>
@@ -290,6 +260,36 @@
   </si>
   <si>
     <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>Reason</t>
@@ -416,7 +416,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -528,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -542,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -598,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -612,7 +612,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -626,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -640,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -654,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -668,7 +668,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -682,7 +682,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -696,7 +696,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -822,7 +822,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -836,7 +836,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -850,7 +850,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -864,7 +864,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -878,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -892,7 +892,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -906,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>
@@ -920,7 +920,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C40" t="n" s="0">
         <v>0.0</v>
@@ -934,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C41" t="n" s="0">
         <v>0.0</v>
@@ -948,7 +948,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>0.0</v>
@@ -962,7 +962,7 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>0.0</v>
@@ -976,7 +976,7 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>0.0</v>
@@ -990,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>0.0</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>0.0</v>
@@ -1018,7 +1018,7 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>0.0</v>
@@ -1032,7 +1032,7 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>0.0</v>
@@ -1046,7 +1046,7 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>0.0</v>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -28,75 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-16</t>
+    <t>2026-01-06</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
     <t>2026-01-07</t>
   </si>
   <si>
@@ -290,6 +227,69 @@
   </si>
   <si>
     <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
   </si>
   <si>
     <t>Reason</t>
@@ -416,7 +416,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -430,7 +430,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>0.0</v>
@@ -444,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>0.0</v>
@@ -458,7 +458,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -472,7 +472,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -486,7 +486,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -500,7 +500,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -514,7 +514,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -528,7 +528,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>0.0</v>
@@ -542,7 +542,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>0.0</v>
@@ -556,7 +556,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -570,7 +570,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -598,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -612,7 +612,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -626,7 +626,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -640,7 +640,7 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>0.0</v>
@@ -654,7 +654,7 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>0.0</v>
@@ -668,7 +668,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -682,7 +682,7 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -696,7 +696,7 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>0.0</v>
@@ -710,7 +710,7 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -724,7 +724,7 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -738,7 +738,7 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -752,7 +752,7 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -766,7 +766,7 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>0.0</v>
@@ -780,7 +780,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>0.0</v>
@@ -794,7 +794,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>0.0</v>
@@ -808,7 +808,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>0.0</v>
@@ -822,7 +822,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C33" t="n" s="0">
         <v>0.0</v>
@@ -836,7 +836,7 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C34" t="n" s="0">
         <v>0.0</v>
@@ -850,7 +850,7 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>0.0</v>
@@ -864,7 +864,7 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>0.0</v>
@@ -878,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>0.0</v>
@@ -892,7 +892,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>0.0</v>
@@ -906,7 +906,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C39" t="n" s="0">
         <v>0.0</v>

--- a/gsc-export-old/Video-Indexing.xlsx
+++ b/gsc-export-old/Video-Indexing.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -28,27 +28,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-06</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
     <t>2026-01-12</t>
   </si>
   <si>
@@ -290,6 +275,27 @@
   </si>
   <si>
     <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
   </si>
   <si>
     <t>Reason</t>
@@ -366,7 +372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,11 +407,11 @@
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>0.0</v>
@@ -458,7 +464,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>0.0</v>
@@ -472,7 +478,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>0.0</v>
@@ -486,7 +492,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>0.0</v>
@@ -500,7 +506,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -514,7 +520,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -556,7 +562,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>0.0</v>
@@ -570,7 +576,7 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -584,7 +590,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -598,7 +604,7 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -612,7 +618,7 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -1598,6 +1604,34 @@
         <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1613,21 +1647,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
@@ -1645,18 +1679,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
